--- a/光伏配储项目/电价数据/2026/吉大站.xlsx
+++ b/光伏配储项目/电价数据/2026/吉大站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55361</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51828</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.86114</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12614</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01986</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.91823</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.71878</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.72823</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.53847</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.59066</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.52406</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.69064</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.69077</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.68121</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51735</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.69863</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.66206</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.68723</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.7014</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54616</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.6994900000000001</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.70726</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.55141</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.7322799999999999</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.82174</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.8581599999999999</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6767300000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.67189</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45222</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73384</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7565499999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.01003</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99449</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08541</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75041</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.69796</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50114</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7835599999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31241</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52306</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.75983</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76773</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74748</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.92814</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.8946900000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04794</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31519</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12338</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.12218</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73411</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.21029</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16902</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09673</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22867</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10508</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24739</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47625</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30514</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23605</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79962</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.41058</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.3541</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28478</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.80336</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16812</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03706</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17645</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51258</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61403</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.5142599999999999</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.5883400000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.49308</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.52281</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.51416</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51412</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.51022</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.5591699999999999</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7687999999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.07353</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83975</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5917100000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48538</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.53861</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50902</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9350700000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.1508</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.77591</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11976</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03759</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.9868899999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7078</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5478999999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56684</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.67965</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15391</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.23107</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47513</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15824</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.6292</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07847</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8180599999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25116</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13598</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28316</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62164</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63836</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57011</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.16101</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16841</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17706</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17161</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.96841</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18756</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20238</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19404</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66888</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.16156</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20558</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.21064</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50695</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41208</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16783</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50944</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26398</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74315</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7648200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9153300000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.60323</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.68508</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.69429</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5330900000000001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57789</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50806</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8417</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.5970700000000001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5890700000000001</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5575800000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.5578500000000001</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.63505</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48758</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.58486</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.52404</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55738</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49649</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.5124099999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50876</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.46217</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.6928099999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8307100000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10793</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87376</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7448400000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70313</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60442</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72915</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16433</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52186</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.67701</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16685</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.62114</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16514</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7927999999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.93967</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16404</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16546</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55948</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47464</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67423</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16549</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02845</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16456</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39285</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23589</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16583</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21568</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20944</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.4014</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26883</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28576</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64847</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.17154</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17429</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78411</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03909</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07839</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09925</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08532</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20456</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16818</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24837</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.9949600000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75429</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71085</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10987</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7223200000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7153099999999999</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.20332</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.68069</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.8547100000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.54111</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.61068</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.22832</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5938300000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.65542</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5874400000000001</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5278099999999999</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.51759</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.51113</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.57824</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48984</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.67636</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.71827</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93267</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16777</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30908</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55146</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66581</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90359</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.86464</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16395</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43972</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77259</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9532200000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.68914</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12237</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48522</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65424</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99612</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10256</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24904</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16845</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.06112</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98178</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02568</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98963</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25177</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.44109</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79308</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.3486</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.23329</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.1912</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84758</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07409</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16086</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12153</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15399</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2547</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31814</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15402</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26951</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18602</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18852</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.1892</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17471</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15227</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17596</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72388</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7261299999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32162</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74361</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49358</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47768</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71639</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8476900000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61475</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.7015800000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72663</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.84524</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.7050700000000001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5506799999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5384500000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59229</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08531</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48217</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51213</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46629</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63318</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48306</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48321</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48736</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.59426</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50582</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48598</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3439</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19094</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96597</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59027</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6474800000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.54574</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.52919</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.54459</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.51373</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.6875599999999999</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.52811</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.5284099999999999</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.51119</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.51202</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.5127699999999999</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07335999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04535</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27265</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08281999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04665</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25325</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44591</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.5933099999999999</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.53961</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.56141</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.5414099999999999</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.5406299999999999</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55731</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.74164</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8743500000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67465</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.64863</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.66749</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.74854</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93936</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.72994</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73162</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88788</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5357799999999999</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08545</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.7316</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72822</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63876</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60292</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72851</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7886599999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78271</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60037</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7417100000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01804</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40614</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84309</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43392</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29771</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.7886799999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.38062</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04498</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.4009</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76531</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44393</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.77436</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8003899999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78504</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8787999999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50198</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41139</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4601</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2185</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54123</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.61663</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.58425</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.5646100000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.57316</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.57975</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5082099999999999</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.58128</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.56109</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.49266</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.51475</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.51835</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.51497</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5149400000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.51593</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.56651</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.47157</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.57241</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.49269</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56367</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66623</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07968</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63855</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5026499999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56925</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59868</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.0014</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33899</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30662</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27478</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55925</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8017300000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57299</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65085</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55059</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95638</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7765700000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7256699999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64212</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57537</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98899</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.9318099999999999</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78885</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54225</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.6712899999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.6708200000000001</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.62254</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6634099999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7046</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.64073</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.66206</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5832000000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.6600900000000001</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.6768099999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.62303</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.67057</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.6888500000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7612599999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.67961</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7581599999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68874</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6864600000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68799</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.6722400000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.6619400000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.62012</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.66111</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.60453</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5437000000000001</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60765</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.55624</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.5577000000000001</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.54313</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.53287</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46895</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57585</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.6095700000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62283</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6807799999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.53524</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.54898</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.52513</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49269</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5130800000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6176699999999999</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7277400000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.87138</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.11167</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93213</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.54504</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11337</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84365</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.94935</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8592799999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63973</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06744</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.5699299999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52242</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.87507</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99524</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.54125</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.19068</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.7837799999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81341</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7409</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73976</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47513</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19614</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51261</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79316</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7490599999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16607</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9213899999999999</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64313</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66764</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70073</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55496</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16402</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61239</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90925</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57686</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33601</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.26052</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22833</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.34216</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.00778</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51903</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60209</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50576</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.75026</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07576</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07371</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98281</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93645</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17402</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15423</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.86251</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.1555</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60765</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9705499999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01578</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15491</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.95041</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99068</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58466</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92415</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98145</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88554</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87317</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79347</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09649</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.5558</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.95997</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.9912799999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74329</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33171</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6084400000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.49441</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50712</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.59196</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49444</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.53247</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8330599999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71433</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.55002</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.56813</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.72966</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8593500000000001</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.5702999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.57441</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.5761799999999999</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.51101</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.5107699999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.55833</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.61833</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.56192</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.46231</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67722</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5423600000000001</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.51089</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50615</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50954</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46972</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.57247</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.52922</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.53576</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.52301</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.5495599999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.49243</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51542</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.50261</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.52364</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.5294099999999999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.5245299999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48588</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.47329</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5541200000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47009</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6029500000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6276900000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84901</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27148</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.1664</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8522000000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70141</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94024</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16797</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12167</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01855</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54187</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44601</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5632200000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.46241</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43938</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50434</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.48523</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.50912</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.50813</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.58047</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.72258</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.05999</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11359</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9911799999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98145</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56585</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54721</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94629</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08622</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78429</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01324</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76829</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64886</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.6416</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.7089</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29846</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.29528</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.01801</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.67946</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.5061</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.6243</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65794</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67131</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66638</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64335</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66784</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20688</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70077</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78257</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69808</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70586</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71401</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63354</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74831</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02168</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13146</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69192</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70036</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69413</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77376</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72392</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8132999999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66665</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46307</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06574</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.5803700000000001</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.49011</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34415</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.45163</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.60033</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17708</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.49099</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46412</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.5105500000000001</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.49761</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44346</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.74719</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49507</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5107699999999999</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51901</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9225099999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47495</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17989</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90226</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7632000000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74679</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51515</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68124</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49599</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.6647999999999999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.52397</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48902</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.70609</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54603</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76149</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76818</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54657</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50161</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7231300000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7626000000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55424</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02054</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48722</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44689</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09487</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12981</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08377</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11236</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12883</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01862</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19441</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14268</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13189</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17435</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84139</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.1913</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84845</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34117</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9038099999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73322</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75774</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.6903</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.3928</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.55907</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.54313</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.53208</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.5378500000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7561100000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37217</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.35406</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.51811</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.6167999999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5132100000000001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5777899999999999</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.59357</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5946399999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51837</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.58914</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.53289</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5779500000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.50587</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46254</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47008</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45712</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.63886</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54828</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.68352</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53867</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02781</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77361</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74133</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27992</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34139</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71796</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64144</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34799</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99483</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59177</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49315</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49463</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53928</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5898</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73346</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17703</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.6910499999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91252</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6647999999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93416</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8805700000000001</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.7449</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71419</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17549</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17667</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42522</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23636</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61651</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20484</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28278</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07722</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39895</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03318</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.66904</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.6395599999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13914</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63342</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52551</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5319400000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8007300000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6685099999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64971</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50856</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06806</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66673</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66332</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.79595</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04903</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16731</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19228</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54601</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15331</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55672</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49767</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47879</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45931</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.5971599999999999</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7563799999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12761</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6895399999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.5544600000000001</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49307</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58065</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47761</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46205</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46314</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.54543</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46763</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47831</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48301</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37005</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.86238</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.48504</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.43284</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23339</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11195</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.6997599999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17372</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26017</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09875</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.68847</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.55884</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8022100000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46575</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48435</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09322</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36604</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.84899</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8067799999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5217200000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75321</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75183</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.5119</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55422</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.74391</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.57345</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7973300000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7530399999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52278</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28632</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28968</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21725</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06153</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.95438</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28448</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.61117</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49132</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5754400000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.74985</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5459400000000001</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5411900000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21401</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75282</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.7512300000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5751799999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98558</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75952</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61838</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75038</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17286</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60078</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62422</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23664</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.8735599999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.88048</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.89907</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15298</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.63885</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.93172</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6789700000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.95672</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.61988</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.638</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.7359</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.62036</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79252</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24391</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03407</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9958899999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.0083</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51465</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34095</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.0481</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75397</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34523</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5568200000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8012699999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7509199999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7527200000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55904</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46884</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62759</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59035</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5564600000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5374099999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47344</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49462</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5571699999999999</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8114600000000001</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.1537</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11925</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03216</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12197</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72582</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.72057</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04299</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06137</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66847</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5554600000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5619299999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5463899999999999</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54113</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6571399999999999</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.5417</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04336</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65415</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54665</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49701</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48056</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48034</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57477</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5550499999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55855</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49596</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51163</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4984</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65711</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15249</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05547</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6583300000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5799500000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15091</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8635900000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.65759</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.14035</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.8130700000000001</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49243</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50963</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49714</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53285</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34434</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.5815499999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58813</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45189</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62579</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58341</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6296799999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00482</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17508</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92432</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9614199999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.01038</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.95147</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.9178200000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94772</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.93162</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91498</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.91731</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.6715</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02629</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.66914</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.02318</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12496</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10682</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.6990499999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92192</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8427899999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9096799999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54178</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66689</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68936</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73776</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78783</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19693</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07705</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01656</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32913</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01221</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11129</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91567</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75175</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.81337</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69184</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55632</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6883400000000001</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7246900000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.68501</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74702</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69513</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46101</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73315</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.51974</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50548</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.99456</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.89166</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00785</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8964500000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01567</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.9986900000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16479</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06792</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.0914</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6656299999999999</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71805</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.70512</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02565</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69802</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75104</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13491</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.23141</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.4325</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.20112</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.36322</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.9848899999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.40111</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.38038</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65472</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.42222</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.42404</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80749</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75527</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80198</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.5600700000000001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7541</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81099</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31352</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00398</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9341</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.96033</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03399</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16261</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06214</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86433</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6934400000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22287</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20878</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20944</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15184</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70355</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09721</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10812</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10815</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13449</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10585</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20116</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.64027</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73168</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6638500000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18519</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.86209</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06605</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03308</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.0506</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03636</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06917</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12817</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05064</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06125</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18422</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16277</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21622</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20336</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26688</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16946</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14352</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12005</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10069</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12683</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17655</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19413</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17471</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07744</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.67427</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61475</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.56584</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5484199999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53109</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31363</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31084</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06776</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47915</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51985</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43843</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43529</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84835</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.56672</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68414</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.69978</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94162</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75264</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94698</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15874</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30672</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44594</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43403</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45943</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54617</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25257</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8512000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.62001</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7006100000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50282</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84433</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8667699999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.21533</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77327</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58068</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62748</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7079299999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.73554</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61049</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20017</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17674</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41144</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17812</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17883</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18413</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10408</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07881</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20743</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10649</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.1928</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05142</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08291</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08306</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54257</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80745</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21394</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84961</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5545599999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5477799999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55757</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17562</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8829900000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49393</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17181</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5094</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694600000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8442000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79518</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85288</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5228700000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54374</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17761</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5553400000000001</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54923</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55035</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.7996</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55506</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7990900000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8490800000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17421</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79867</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6835399999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05257</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17604</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17748</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17541</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82414</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7325700000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64537</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68492</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7312000000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83478</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6154700000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8069400000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75662</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13687</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75112</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60945</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63667</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.63858</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6173099999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61461</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.70409</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67083</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8140499999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70408</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
